--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -10824,6 +10824,151 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10857,7 +11002,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10940,7 +11085,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -10950,7 +11095,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -10969,6 +10969,151 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>44</v>
+      </c>
+      <c r="O72" t="n">
+        <v>44</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.01260616778418529</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11002,7 +11147,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11230,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -11095,7 +11240,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -11147,7 +11292,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2584</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -11114,6 +11114,151 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11147,7 +11292,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11375,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -11240,7 +11385,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -11259,6 +11259,151 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>59</v>
+      </c>
+      <c r="O74" t="n">
+        <v>59</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.01690372498333937</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11292,7 +11437,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11520,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -11385,7 +11530,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -11437,7 +11582,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2628</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -11404,6 +11404,296 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>362</v>
+      </c>
+      <c r="O76" t="n">
+        <v>362</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.1037143804062517</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11437,7 +11727,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -11520,7 +11810,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -11530,7 +11820,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -11582,7 +11872,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2687</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -11694,6 +11694,296 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>295</v>
+      </c>
+      <c r="O78" t="n">
+        <v>295</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.08451862491669687</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11727,7 +12017,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -11810,7 +12100,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -11820,7 +12110,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -11872,7 +12162,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3049</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -11984,6 +11984,151 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12017,7 +12162,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12245,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -12110,7 +12255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1077,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1378,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1679,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +1980,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2582,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2883,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3184,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4689,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +4990,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5592,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6194,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6796,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6989,6 +7094,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7279,6 +7389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7569,6 +7684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7859,6 +7979,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8149,6 +8274,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8439,6 +8569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8729,6 +8864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9019,6 +9159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9309,6 +9454,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9599,6 +9749,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9889,6 +10044,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10179,6 +10339,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10469,6 +10634,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10759,6 +10929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11049,6 +11224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11339,6 +11519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11629,6 +11814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11919,6 +12109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12126,6 +12321,156 @@
       <c r="BC79" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>347</v>
+      </c>
+      <c r="O80" t="n">
+        <v>347</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.09941682320709769</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12507,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -12245,7 +12590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -12255,7 +12600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -12307,7 +12652,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3344</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -12474,6 +12474,151 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12507,7 +12652,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -12590,7 +12735,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -12600,7 +12745,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d095/2026-2029.xlsx
+++ b/diseases/d095/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -1066,9 +1063,6 @@
       <c r="O4" t="n">
         <v>232</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.06646888468024974</v>
       </c>
@@ -1367,9 +1361,6 @@
       <c r="O6" t="n">
         <v>293</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.08394561729014299</v>
       </c>
@@ -1668,9 +1659,6 @@
       <c r="O8" t="n">
         <v>100</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.02865038132769385</v>
       </c>
@@ -1969,9 +1957,6 @@
       <c r="O10" t="n">
         <v>91</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.0260718470082014</v>
       </c>
@@ -2270,9 +2255,6 @@
       <c r="O12" t="n">
         <v>100</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.02865038132769385</v>
       </c>
@@ -2571,9 +2553,6 @@
       <c r="O14" t="n">
         <v>75</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.02148778599577039</v>
       </c>
@@ -2872,9 +2851,6 @@
       <c r="O16" t="n">
         <v>42</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01203316015763142</v>
       </c>
@@ -3173,9 +3149,6 @@
       <c r="O18" t="n">
         <v>61</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.01747673260989325</v>
       </c>
@@ -3474,9 +3447,6 @@
       <c r="O20" t="n">
         <v>71</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.02034177074266263</v>
       </c>
@@ -3775,9 +3745,6 @@
       <c r="O22" t="n">
         <v>47</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01346567922401611</v>
       </c>
@@ -4076,9 +4043,6 @@
       <c r="O24" t="n">
         <v>45</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.01289267159746223</v>
       </c>
@@ -4377,9 +4341,6 @@
       <c r="O26" t="n">
         <v>25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.007162595331923463</v>
       </c>
@@ -4678,9 +4639,6 @@
       <c r="O28" t="n">
         <v>64</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.01833624404972407</v>
       </c>
@@ -4979,9 +4937,6 @@
       <c r="O30" t="n">
         <v>64</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01833624404972407</v>
       </c>
@@ -5280,9 +5235,6 @@
       <c r="O32" t="n">
         <v>82</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02349331268870896</v>
       </c>
@@ -5581,9 +5533,6 @@
       <c r="O34" t="n">
         <v>57</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.0163307173567855</v>
       </c>
@@ -5882,9 +5831,6 @@
       <c r="O36" t="n">
         <v>100</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.02865038132769385</v>
       </c>
@@ -6183,9 +6129,6 @@
       <c r="O38" t="n">
         <v>73</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.02091477836921651</v>
       </c>
@@ -6484,9 +6427,6 @@
       <c r="O40" t="n">
         <v>68</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.01948225930283182</v>
       </c>
@@ -6785,9 +6725,6 @@
       <c r="O42" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -12616,6 +12553,156 @@
       <c r="BC81" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D095</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Coccidioidomycosis</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>球孢子菌病</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Fungal</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>209</v>
+      </c>
+      <c r="O82" t="n">
+        <v>209</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.05987929697488016</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12739,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12822,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -12745,7 +12832,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -12797,7 +12884,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3691</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="16">
